--- a/datf_core/test/testprotocol/testselection_template.xlsx
+++ b/datf_core/test/testprotocol/testselection_template.xlsx
@@ -747,7 +747,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>test/s2t/source_parquet_target_parquet_s2t_1.xlsx</t>
+          <t>test/s2t/s2t_1_parquet_parquet_mismatch.xlsx</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -755,7 +755,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI2" t="n">
         <v>5</v>
       </c>
@@ -813,7 +817,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>test/s2t/source_parquet_target_parquet_s2t_2.xlsx</t>
+          <t>test/s2t/s2t_2_parquet_parquet_match.xlsx</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -821,7 +825,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI3" t="n">
         <v>5</v>
       </c>
@@ -887,7 +895,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI4" t="n">
         <v>5</v>
       </c>
@@ -953,7 +965,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI5" t="n">
         <v>5</v>
       </c>
@@ -1011,7 +1027,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>test/s2t/source_csv_target_parquet_s2t_5.xlsx</t>
+          <t>test/s2t/s2t_5_csv_parquet_match.xlsx</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1019,7 +1035,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI6" t="n">
         <v>5</v>
       </c>
@@ -1077,7 +1097,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>test/s2t/source_csv_target_parquet_s2t_6_mismatch.xlsx</t>
+          <t>test/s2t/s2t_6_csv_parquet_mismatch.xlsx</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1085,7 +1105,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI7" t="n">
         <v>5</v>
       </c>
@@ -1151,7 +1175,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI8" t="n">
         <v>5</v>
       </c>
@@ -1217,7 +1245,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI9" t="n">
         <v>5</v>
       </c>
@@ -1345,7 +1377,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>test/s2t/source_json_target_parquet_s2t_10_mismatch.xlsx</t>
+          <t>test/s2t/s2t_10_json_parquet_match.xlsx</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1353,7 +1385,11 @@
           <t>source_to_target</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
       <c r="AI11" t="n">
         <v>5</v>
       </c>
